--- a/data/trans_camb/P1408-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P1408-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-2,28</t>
+          <t>-2,08</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,97</t>
+          <t>0,84</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,7</t>
+          <t>-0,66</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,18; -0,03</t>
+          <t>-5,12; 0,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 1,98</t>
+          <t>-4,19; 1,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,25; -0,27</t>
+          <t>-4,86; 0,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 3,49</t>
+          <t>-0,4; 3,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 1,26</t>
+          <t>-0,88; 1,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 2,16</t>
+          <t>-0,41; 1,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 0,85</t>
+          <t>-2,17; 0,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 1,12</t>
+          <t>-2,0; 1,28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 0,63</t>
+          <t>-2,15; 0,5</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-64,5%</t>
+          <t>-58,88%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>246,99%</t>
+          <t>213,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-34,79%</t>
+          <t>-32,94%</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-92,33; 20,74</t>
+          <t>-93,08; 25,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-77,88; 121,13</t>
+          <t>-80,67; 118,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-90,56; -1,73</t>
+          <t>-88,57; 20,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-80,29; 93,81</t>
+          <t>-79,81; 90,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-75,68; 106,58</t>
+          <t>-71,86; 112,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-69,78; 67,11</t>
+          <t>-72,74; 47,41</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-2,96</t>
+          <t>-2,93</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-1,82</t>
+          <t>-1,8</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,38</t>
+          <t>-2,36</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 0,86</t>
+          <t>-4,26; 0,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 0,18</t>
+          <t>-4,91; 0,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,56; -0,82</t>
+          <t>-5,67; -0,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,68; -0,68</t>
+          <t>-4,38; -0,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,2; -0,34</t>
+          <t>-4,37; -0,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 0,12</t>
+          <t>-3,72; 0,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,96; -0,58</t>
+          <t>-3,85; -0,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,8; -0,6</t>
+          <t>-3,89; -0,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,89; -0,98</t>
+          <t>-4,02; -0,87</t>
         </is>
       </c>
     </row>
@@ -956,22 +956,22 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>-59,59%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>-67,43%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>-60,23%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-67,43%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-60,23%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-49,0%</t>
+          <t>-48,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-55,33%</t>
+          <t>-54,79%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-69,04; 26,56</t>
+          <t>-66,75; 29,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-75,14; 9,2</t>
+          <t>-72,91; 9,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-81,38; -17,98</t>
+          <t>-82,7; -17,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-89,25; -13,27</t>
+          <t>-88,56; -13,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-85,6; -1,21</t>
+          <t>-85,16; 0,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-74,37; 12,29</t>
+          <t>-75,18; 8,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-72,21; -14,56</t>
+          <t>-72,57; -14,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-73,28; -17,13</t>
+          <t>-71,62; -14,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-73,74; -28,25</t>
+          <t>-73,88; -22,6</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,84</t>
+          <t>-0,88</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,28</t>
+          <t>2,29</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>0,75</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 0,69</t>
+          <t>-5,02; 0,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,55; -0,52</t>
+          <t>-5,72; -0,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 1,83</t>
+          <t>-3,95; 1,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 2,32</t>
+          <t>-0,99; 2,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 1,64</t>
+          <t>-1,29; 1,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,89</t>
+          <t>0,41; 3,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 1,11</t>
+          <t>-2,18; 1,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 0,06</t>
+          <t>-2,94; 0,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 2,35</t>
+          <t>-0,88; 2,21</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-20,65%</t>
+          <t>-21,42%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>248,38%</t>
+          <t>249,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,34%</t>
         </is>
       </c>
     </row>
@@ -1215,22 +1215,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-82,32; 34,56</t>
+          <t>-83,06; 50,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-90,77; -6,82</t>
+          <t>-90,29; 7,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-62,63; 86,75</t>
+          <t>-67,07; 66,46</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-78,62; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,16; —</t>
+          <t>-7,11; 1221,1</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-68,04; 72,42</t>
+          <t>-65,51; 80,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-82,21; 17,29</t>
+          <t>-83,31; 20,57</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-25,54; 160,29</t>
+          <t>-25,77; 136,86</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,17</t>
+          <t>-0,41</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,05</t>
+          <t>1,62</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,32</t>
+          <t>0,61</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 1,36</t>
+          <t>-4,28; 1,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 0,82</t>
+          <t>-4,34; 0,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 2,75</t>
+          <t>-3,08; 2,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 3,0</t>
+          <t>-1,12; 3,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 1,36</t>
+          <t>-2,17; 1,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 3,82</t>
+          <t>-0,24; 4,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 1,62</t>
+          <t>-1,98; 1,4</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 0,53</t>
+          <t>-2,61; 0,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 2,26</t>
+          <t>-1,16; 2,76</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-4,06%</t>
+          <t>-9,68%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>20,76%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-73,34; 73,21</t>
+          <t>-73,41; 42,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-75,35; 30,86</t>
+          <t>-75,25; 33,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-56,39; 97,02</t>
+          <t>-57,06; 95,71</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-44,36; 377,4</t>
+          <t>-48,82; 400,21</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-82,09; 175,5</t>
+          <t>-83,16; 183,44</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-38,67; 462,42</t>
+          <t>-25,44; 617,36</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-56,38; 85,13</t>
+          <t>-54,02; 71,03</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-67,1; 35,05</t>
+          <t>-66,78; 29,54</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-39,96; 109,1</t>
+          <t>-33,75; 128,01</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-2,23</t>
+          <t>-2,39</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-2,61</t>
+          <t>-2,68</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-2,43</t>
+          <t>-2,54</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 0,32</t>
+          <t>-6,09; 0,3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 0,82</t>
+          <t>-5,51; 0,87</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 0,65</t>
+          <t>-5,85; 0,47</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,54; -1,1</t>
+          <t>-7,15; -1,39</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,19; -0,55</t>
+          <t>-6,58; -0,54</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,17; -0,04</t>
+          <t>-6,73; -0,16</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-5,62; -1,18</t>
+          <t>-5,54; -1,24</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,27; -0,51</t>
+          <t>-5,16; -0,69</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,94; -0,34</t>
+          <t>-5,05; -0,68</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-53,3%</t>
+          <t>-56,97%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-61,66%</t>
+          <t>-63,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-57,8%</t>
+          <t>-60,37%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 40,37</t>
+          <t>-100,0; 52,11</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-88,18; 58,46</t>
+          <t>-86,11; 77,59</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-85,59; 44,26</t>
+          <t>-87,27; 53,37</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 18,24</t>
+          <t>-100,0; -30,61</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 14,97</t>
+          <t>-100,0; 14,86</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-87,98; 8,38</t>
+          <t>-89,01; 7,19</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-94,37; -25,89</t>
+          <t>-94,19; -30,36</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-85,82; -7,83</t>
+          <t>-84,15; -11,93</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-78,84; -8,34</t>
+          <t>-80,76; -18,96</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2,56</t>
+          <t>2,48</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,22 +1729,22 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
+          <t>2,38</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>1,18</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>-0,09</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
           <t>2,44</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>1,18</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>-0,09</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>2,52</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 6,12</t>
+          <t>-0,2; 5,99</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 1,56</t>
+          <t>-2,71; 1,57</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 5,13</t>
+          <t>-0,05; 4,86</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 1,58</t>
+          <t>-2,18; 1,41</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 2,46</t>
+          <t>-1,67; 2,6</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,49</t>
+          <t>0,22; 4,37</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 3,16</t>
+          <t>-0,58; 3,03</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 1,47</t>
+          <t>-1,58; 1,56</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,02</t>
+          <t>0,93; 4,15</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>123,05%</t>
+          <t>119,22%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>200,69%</t>
+          <t>195,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>153,37%</t>
+          <t>148,74%</t>
         </is>
       </c>
     </row>
@@ -1863,17 +1863,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-26,5; 576,64</t>
+          <t>-24,01; 554,47</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-86,35; 217,49</t>
+          <t>-87,97; 162,6</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-18,24; 546,23</t>
+          <t>-12,87; 551,18</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1888,22 +1888,22 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 999,1</t>
+          <t>-14,76; 1094,39</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-33,44; 307,6</t>
+          <t>-31,83; 325,22</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-65,14; 169,65</t>
+          <t>-68,43; 175,69</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>28,94; 445,61</t>
+          <t>22,62; 467,95</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-1,69</t>
+          <t>-1,84</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-0,75</t>
+          <t>-0,11</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-1,22</t>
+          <t>-0,95</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-5,06; -1,61</t>
+          <t>-5,27; -1,72</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,62; -0,92</t>
+          <t>-4,69; -0,91</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 0,22</t>
+          <t>-3,78; 0,2</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,98; -0,78</t>
+          <t>-4,04; -0,82</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,69; -0,34</t>
+          <t>-3,54; -0,08</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 1,25</t>
+          <t>-2,06; 1,77</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-4,1; -1,67</t>
+          <t>-4,03; -1,68</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,57; -1,08</t>
+          <t>-3,68; -1,04</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 0,12</t>
+          <t>-2,3; 0,46</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-38,18%</t>
+          <t>-41,57%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-22,38%</t>
+          <t>-3,16%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-31,5%</t>
+          <t>-24,58%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-89,99; -46,0</t>
+          <t>-90,93; -47,88</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-83,1; -21,1</t>
+          <t>-83,12; -23,32</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-65,38; 10,79</t>
+          <t>-68,06; 11,12</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-87,18; -19,99</t>
+          <t>-86,44; -25,15</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-81,38; -6,27</t>
+          <t>-78,99; 9,42</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-66,55; 50,61</t>
+          <t>-48,2; 76,62</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-86,12; -53,27</t>
+          <t>-84,49; -50,78</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-75,56; -30,15</t>
+          <t>-76,79; -30,19</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-61,92; 2,53</t>
+          <t>-48,07; 16,49</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-2,9</t>
+          <t>-2,39</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-1,46</t>
+          <t>-1,5</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-2,22</t>
+          <t>-1,93</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,63; -1,12</t>
+          <t>-4,57; -1,05</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4,73; -1,24</t>
+          <t>-4,66; -1,27</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-5,1; -1,27</t>
+          <t>-4,24; -0,63</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-4,62; -1,73</t>
+          <t>-4,76; -1,64</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,13; -0,92</t>
+          <t>-4,12; -0,76</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 0,12</t>
+          <t>-3,47; -0,14</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-4,17; -1,77</t>
+          <t>-4,1; -1,87</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,81; -1,37</t>
+          <t>-3,81; -1,57</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,64; -1,13</t>
+          <t>-3,17; -0,86</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-66,39%</t>
+          <t>-54,83%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-39,6%</t>
+          <t>-40,46%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-55,24%</t>
+          <t>-48,06%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-83,48; -23,98</t>
+          <t>-83,25; -22,2</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-82,82; -33,17</t>
+          <t>-80,64; -26,93</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-87,9; -36,5</t>
+          <t>-74,55; -14,99</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-94,97; -55,3</t>
+          <t>-94,26; -50,45</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-85,23; -28,94</t>
+          <t>-85,24; -22,71</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-65,85; 9,13</t>
+          <t>-68,72; -3,48</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-85,5; -50,08</t>
+          <t>-84,63; -54,09</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-79,01; -41,82</t>
+          <t>-78,61; -45,8</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-73,86; -32,58</t>
+          <t>-65,17; -24,42</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-1,73</t>
+          <t>-1,6</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-0,29</t>
+          <t>-0,14</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-1,0</t>
+          <t>-0,86</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-2,81; -1,05</t>
+          <t>-2,95; -1,17</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,04; -1,33</t>
+          <t>-3,07; -1,44</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-2,62; -0,84</t>
+          <t>-2,38; -0,78</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2,26; -0,86</t>
+          <t>-2,12; -0,83</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,13; -0,8</t>
+          <t>-2,18; -0,73</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 0,47</t>
+          <t>-0,91; 0,54</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-2,29; -1,19</t>
+          <t>-2,37; -1,22</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-2,35; -1,29</t>
+          <t>-2,36; -1,28</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-1,61; -0,33</t>
+          <t>-1,41; -0,32</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-41,68%</t>
+          <t>-38,58%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-10,53%</t>
+          <t>-5,11%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-29,15%</t>
+          <t>-25,12%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-61,18; -28,96</t>
+          <t>-63,61; -30,64</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-65,19; -36,12</t>
+          <t>-65,26; -38,43</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-56,71; -23,44</t>
+          <t>-51,62; -21,49</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-70,45; -35,17</t>
+          <t>-68,85; -35,09</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-68,41; -32,66</t>
+          <t>-68,29; -32,1</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-34,09; 20,86</t>
+          <t>-29,05; 23,27</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-61,51; -38,14</t>
+          <t>-62,78; -39,34</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-62,47; -40,49</t>
+          <t>-63,3; -41,46</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-42,91; -10,66</t>
+          <t>-38,19; -10,22</t>
         </is>
       </c>
     </row>
